--- a/server/server/uploads/Transit-Shipment---Copy.xlsx
+++ b/server/server/uploads/Transit-Shipment---Copy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Pictures\reports shipment 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FE4A09-90CD-4075-AD31-792A1BD7616A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77C9935-D218-43BF-8B68-35E8A23EB3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
   <si>
     <t xml:space="preserve">                            Please review the Example tab before you complete this sheet</t>
   </si>
@@ -241,13 +241,25 @@
   </si>
   <si>
     <t>CRM-CSB5-Black-Red</t>
+  </si>
+  <si>
+    <t>BLR7</t>
+  </si>
+  <si>
+    <t>BLR8</t>
+  </si>
+  <si>
+    <t>BOM5</t>
+  </si>
+  <si>
+    <t>AMD2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -330,6 +342,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -487,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -537,6 +554,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -800,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I886"/>
+  <dimension ref="A1:I889"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -958,8 +978,8 @@
       <c r="B10" s="16">
         <v>16</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>18</v>
+      <c r="C10" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -969,14 +989,14 @@
       <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:9" thickBot="1">
-      <c r="A11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="17">
-        <v>6</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>18</v>
+      <c r="A11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="16">
+        <v>52</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -986,14 +1006,14 @@
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9" thickBot="1">
-      <c r="A12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="17">
-        <v>42</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>18</v>
+      <c r="A12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="16">
+        <v>44</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -1003,14 +1023,14 @@
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9" thickBot="1">
-      <c r="A13" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="17">
-        <v>15</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>18</v>
+      <c r="A13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="16">
+        <v>46</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -1021,10 +1041,10 @@
     </row>
     <row r="14" spans="1:9" thickBot="1">
       <c r="A14" s="17" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B14" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>18</v>
@@ -1038,10 +1058,10 @@
     </row>
     <row r="15" spans="1:9" thickBot="1">
       <c r="A15" s="17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" s="17">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>18</v>
@@ -1055,10 +1075,10 @@
     </row>
     <row r="16" spans="1:9" thickBot="1">
       <c r="A16" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>18</v>
@@ -1072,10 +1092,10 @@
     </row>
     <row r="17" spans="1:9" thickBot="1">
       <c r="A17" s="17" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B17" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>18</v>
@@ -1089,10 +1109,10 @@
     </row>
     <row r="18" spans="1:9" thickBot="1">
       <c r="A18" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>18</v>
@@ -1106,10 +1126,10 @@
     </row>
     <row r="19" spans="1:9" thickBot="1">
       <c r="A19" s="17" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="B19" s="17">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>18</v>
@@ -1123,10 +1143,10 @@
     </row>
     <row r="20" spans="1:9" thickBot="1">
       <c r="A20" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="17">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>18</v>
@@ -1140,10 +1160,10 @@
     </row>
     <row r="21" spans="1:9" thickBot="1">
       <c r="A21" s="17" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B21" s="17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>18</v>
@@ -1157,10 +1177,10 @@
     </row>
     <row r="22" spans="1:9" thickBot="1">
       <c r="A22" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="17">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>18</v>
@@ -1174,7 +1194,7 @@
     </row>
     <row r="23" spans="1:9" thickBot="1">
       <c r="A23" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B23" s="17">
         <v>20</v>
@@ -1191,10 +1211,10 @@
     </row>
     <row r="24" spans="1:9" thickBot="1">
       <c r="A24" s="17" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B24" s="17">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>18</v>
@@ -1208,10 +1228,10 @@
     </row>
     <row r="25" spans="1:9" thickBot="1">
       <c r="A25" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" s="17">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>18</v>
@@ -1225,10 +1245,10 @@
     </row>
     <row r="26" spans="1:9" thickBot="1">
       <c r="A26" s="17" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B26" s="17">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>18</v>
@@ -1242,10 +1262,10 @@
     </row>
     <row r="27" spans="1:9" thickBot="1">
       <c r="A27" s="17" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B27" s="17">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>18</v>
@@ -1259,10 +1279,10 @@
     </row>
     <row r="28" spans="1:9" thickBot="1">
       <c r="A28" s="17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B28" s="17">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>18</v>
@@ -1276,10 +1296,10 @@
     </row>
     <row r="29" spans="1:9" thickBot="1">
       <c r="A29" s="17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B29" s="17">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>18</v>
@@ -1293,10 +1313,10 @@
     </row>
     <row r="30" spans="1:9" thickBot="1">
       <c r="A30" s="17" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B30" s="17">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>18</v>
@@ -1310,10 +1330,10 @@
     </row>
     <row r="31" spans="1:9" thickBot="1">
       <c r="A31" s="17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31" s="17">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>18</v>
@@ -1327,7 +1347,7 @@
     </row>
     <row r="32" spans="1:9" thickBot="1">
       <c r="A32" s="17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B32" s="17">
         <v>10</v>
@@ -1344,7 +1364,7 @@
     </row>
     <row r="33" spans="1:9" thickBot="1">
       <c r="A33" s="17" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="B33" s="17">
         <v>10</v>
@@ -1361,10 +1381,10 @@
     </row>
     <row r="34" spans="1:9" thickBot="1">
       <c r="A34" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B34" s="17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>18</v>
@@ -1378,7 +1398,7 @@
     </row>
     <row r="35" spans="1:9" thickBot="1">
       <c r="A35" s="17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B35" s="17">
         <v>10</v>
@@ -1395,10 +1415,10 @@
     </row>
     <row r="36" spans="1:9" thickBot="1">
       <c r="A36" s="17" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B36" s="17">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>18</v>
@@ -1412,10 +1432,10 @@
     </row>
     <row r="37" spans="1:9" thickBot="1">
       <c r="A37" s="17" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="B37" s="17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>18</v>
@@ -1429,10 +1449,10 @@
     </row>
     <row r="38" spans="1:9" thickBot="1">
       <c r="A38" s="17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>18</v>
@@ -1446,10 +1466,10 @@
     </row>
     <row r="39" spans="1:9" thickBot="1">
       <c r="A39" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" s="17">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>18</v>
@@ -1463,10 +1483,10 @@
     </row>
     <row r="40" spans="1:9" thickBot="1">
       <c r="A40" s="17" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="B40" s="17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>18</v>
@@ -1480,7 +1500,7 @@
     </row>
     <row r="41" spans="1:9" thickBot="1">
       <c r="A41" s="17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B41" s="17">
         <v>20</v>
@@ -1497,10 +1517,10 @@
     </row>
     <row r="42" spans="1:9" thickBot="1">
       <c r="A42" s="17" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B42" s="17">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>18</v>
@@ -1514,10 +1534,10 @@
     </row>
     <row r="43" spans="1:9" thickBot="1">
       <c r="A43" s="17" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B43" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>18</v>
@@ -1531,10 +1551,10 @@
     </row>
     <row r="44" spans="1:9" thickBot="1">
       <c r="A44" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="17">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>18</v>
@@ -1548,10 +1568,10 @@
     </row>
     <row r="45" spans="1:9" thickBot="1">
       <c r="A45" s="17" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B45" s="17">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>18</v>
@@ -1565,10 +1585,10 @@
     </row>
     <row r="46" spans="1:9" thickBot="1">
       <c r="A46" s="17" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B46" s="17">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>18</v>
@@ -1582,10 +1602,10 @@
     </row>
     <row r="47" spans="1:9" thickBot="1">
       <c r="A47" s="17" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B47" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>18</v>
@@ -1599,10 +1619,10 @@
     </row>
     <row r="48" spans="1:9" thickBot="1">
       <c r="A48" s="17" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B48" s="17">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>18</v>
@@ -1616,10 +1636,10 @@
     </row>
     <row r="49" spans="1:9" thickBot="1">
       <c r="A49" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49" s="17">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>18</v>
@@ -1633,10 +1653,10 @@
     </row>
     <row r="50" spans="1:9" thickBot="1">
       <c r="A50" s="17" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B50" s="17">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>18</v>
@@ -1650,10 +1670,10 @@
     </row>
     <row r="51" spans="1:9" thickBot="1">
       <c r="A51" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B51" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>18</v>
@@ -1667,10 +1687,10 @@
     </row>
     <row r="52" spans="1:9" thickBot="1">
       <c r="A52" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B52" s="17">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>18</v>
@@ -1684,10 +1704,10 @@
     </row>
     <row r="53" spans="1:9" thickBot="1">
       <c r="A53" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B53" s="17">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>18</v>
@@ -1701,10 +1721,10 @@
     </row>
     <row r="54" spans="1:9" thickBot="1">
       <c r="A54" s="17" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B54" s="17">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>18</v>
@@ -1718,10 +1738,10 @@
     </row>
     <row r="55" spans="1:9" thickBot="1">
       <c r="A55" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B55" s="17">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>18</v>
@@ -1735,10 +1755,10 @@
     </row>
     <row r="56" spans="1:9" thickBot="1">
       <c r="A56" s="17" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B56" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>18</v>
@@ -1752,10 +1772,10 @@
     </row>
     <row r="57" spans="1:9" thickBot="1">
       <c r="A57" s="17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B57" s="17">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>18</v>
@@ -1767,45 +1787,63 @@
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
     </row>
-    <row r="58" spans="1:9" ht="13.5" thickBot="1">
+    <row r="58" spans="1:9" thickBot="1">
       <c r="A58" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B58" s="17">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" ht="13.5" thickBot="1">
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+    </row>
+    <row r="59" spans="1:9" thickBot="1">
       <c r="A59" s="17" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B59" s="17">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" ht="13.5" thickBot="1">
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+    </row>
+    <row r="60" spans="1:9" thickBot="1">
       <c r="A60" s="17" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B60" s="17">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>18</v>
       </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
     </row>
     <row r="61" spans="1:9" ht="13.5" thickBot="1">
       <c r="A61" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B61" s="17">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>18</v>
@@ -1813,7 +1851,7 @@
     </row>
     <row r="62" spans="1:9" ht="13.5" thickBot="1">
       <c r="A62" s="17" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B62" s="17">
         <v>30</v>
@@ -1822,31 +1860,49 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15">
-      <c r="A63" s="14" t="s">
+    <row r="63" spans="1:9" ht="13.5" thickBot="1">
+      <c r="A63" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="17">
+        <v>30</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="13.5" thickBot="1">
+      <c r="A64" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B63" s="14">
+      <c r="B64" s="17">
+        <v>30</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A65" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="17">
+        <v>30</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15">
+      <c r="A66" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="14">
         <v>10</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C66" s="14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="15">
-      <c r="A64" s="14"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-    </row>
-    <row r="65" spans="1:3" ht="15">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-    </row>
-    <row r="66" spans="1:3" ht="15">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
     </row>
     <row r="67" spans="1:3" ht="15">
       <c r="A67" s="14"/>
@@ -2594,18 +2650,18 @@
       <c r="C215" s="14"/>
     </row>
     <row r="216" spans="1:3" ht="15">
-      <c r="A216" s="15"/>
-      <c r="B216" s="15"/>
+      <c r="A216" s="14"/>
+      <c r="B216" s="14"/>
       <c r="C216" s="14"/>
     </row>
     <row r="217" spans="1:3" ht="15">
-      <c r="A217" s="15"/>
-      <c r="B217" s="15"/>
+      <c r="A217" s="14"/>
+      <c r="B217" s="14"/>
       <c r="C217" s="14"/>
     </row>
     <row r="218" spans="1:3" ht="15">
-      <c r="A218" s="15"/>
-      <c r="B218" s="15"/>
+      <c r="A218" s="14"/>
+      <c r="B218" s="14"/>
       <c r="C218" s="14"/>
     </row>
     <row r="219" spans="1:3" ht="15">
@@ -5947,6 +6003,21 @@
       <c r="A886" s="15"/>
       <c r="B886" s="15"/>
       <c r="C886" s="14"/>
+    </row>
+    <row r="887" spans="1:3" ht="15">
+      <c r="A887" s="15"/>
+      <c r="B887" s="15"/>
+      <c r="C887" s="14"/>
+    </row>
+    <row r="888" spans="1:3" ht="15">
+      <c r="A888" s="15"/>
+      <c r="B888" s="15"/>
+      <c r="C888" s="14"/>
+    </row>
+    <row r="889" spans="1:3" ht="15">
+      <c r="A889" s="15"/>
+      <c r="B889" s="15"/>
+      <c r="C889" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5955,6 +6026,7 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A8:C8"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
